--- a/logs/token_usage.xlsx
+++ b/logs/token_usage.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="usage" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="projects" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,10 +28,10 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,10 +56,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -424,18 +425,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,221 +497,868 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>— Данные начинаются с 2026-06-13 21:06 (локальное); хвост вечера 13.06 (293 ответа, ~30 млн токенов) не образует полного окна и в таблицу не входит.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>— Сессий — уникальные сессии периода, коснувшиеся модели; одна сессия может использовать несколько моделей, поэтому строка ИТОГО — уникальные сессии периода, не сумма строк выше.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>— Cache read, % — доля кэш-чтений в токенах строки; Output/запрос — средний выход на запрос; $/запрос и $/сессию — стоимость строки на её запросы/сессии; Доля стоимости, % — от итога периода.</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Период</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Запросов</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Output</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Cache write</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Токены всего</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Стоимость по API, $</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>— Лист projects — та же статистика в разрезе проектов (каталогов ~/.claude/projects), отсортировано по стоимости.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14.06.2026-14.07.2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Haiku</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>894</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>39981</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>379130</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>3723871</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>37694487</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>41837469</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10.36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>14.06.2026-14.07.2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Sonnet</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>11735</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>994918</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>6998103</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>58542938</v>
-      </c>
-      <c r="G12" s="3" t="n">
-        <v>2389456064</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>2455992023</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1044.33</v>
-      </c>
-    </row>
+          <t>— Данные начинаются с 2026-06-13 21:06 (локальное); первое окно 14.05.2026-14.06.2026 из-за этого неполное (только вечер 13.06).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>14.06.2026-14.07.2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Opus</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>1933</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>753138</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2140997</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>17579863</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>324661964</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>345135962</v>
-      </c>
-      <c r="I13" t="n">
-        <v>329.5</v>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Запросов</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Сессий</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Cache write</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Токены всего</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Cache read, %</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Output/запрос</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Стоимость по API, $</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>$/запрос</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>$/сессию</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>Доля стоимости, %</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14.06.2026-14.07.2026</t>
+          <t>14.05.2026-14.06.2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fable</t>
+          <t>Sonnet</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>5565</v>
+        <v>293</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>932714</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>6229760</v>
+        <v>587</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>48451946</v>
+        <v>330161</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1188491178</v>
+        <v>940158</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1244105598</v>
-      </c>
-      <c r="I14" t="n">
-        <v>2114.96</v>
+        <v>29047611</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>30318517</v>
+      </c>
+      <c r="J14" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>14.05.2026-14.06.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>587</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>330161</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>940158</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>29047611</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>30318517</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1127</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>0.0587</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>14.06.2026-14.07.2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Haiku</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>894</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>39981</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>379130</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>3723871</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>37694487</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>41837469</v>
+      </c>
+      <c r="J16" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="K16" t="n">
+        <v>424</v>
+      </c>
+      <c r="L16" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sonnet</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>11735</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>108</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>994918</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>6998103</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>58542938</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>2389456064</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>2455992023</v>
+      </c>
+      <c r="J17" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>596</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1044.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="N17" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="O17" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Opus</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1933</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>753138</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2140997</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>17579863</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>324661964</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>345135962</v>
+      </c>
+      <c r="J18" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L18" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fable</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>5565</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>932714</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>6229760</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>48451946</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>1188491178</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>1244105598</v>
+      </c>
+      <c r="J19" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1119</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2114.96</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N19" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="O19" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C20" s="4" t="n">
         <v>20127</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D20" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>2720751</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>15747990</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>128298618</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>3940303693</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I20" s="4" t="n">
         <v>4087071052</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="J20" s="2" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>782</v>
+      </c>
+      <c r="L20" s="2" t="n">
         <v>3499.14</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>0.1739</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Разрез по проектам (каталоги ~/.claude/projects); методика — на листе usage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Период</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Проект</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Запросов</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Сессий</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Cache write</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Токены всего</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Стоимость по API, $</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Доля стоимости, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>14.05.2026-14.06.2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D--Dog</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>587</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>330161</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>940158</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>29047611</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>30318517</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>14.05.2026-14.06.2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>293</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>587</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>330161</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>940158</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>29047611</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>30318517</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-Operating-System-for-LLMs</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>7513</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1460396</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>7569878</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>54622327</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1277020063</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1340672664</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1968.04</v>
+      </c>
+      <c r="K6" t="n">
+        <v>56.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>D--Dog</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>7050</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>323446</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>4301976</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>46586110</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1910623243</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1961834775</v>
+      </c>
+      <c r="J7" t="n">
+        <v>852.72</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D--AO3-tests</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>5327</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>823947</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>3719000</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>26243011</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>730198113</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>760984071</v>
+      </c>
+      <c r="J8" t="n">
+        <v>663.47</v>
+      </c>
+      <c r="K8" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-fresh-project</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>61958</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>86022</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>495382</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>13632637</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>14275999</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-From-Zero</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>109</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>51004</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>71114</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>351788</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>8829637</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>9303543</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>20127</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>2720751</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>15747990</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>128298618</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>3940303693</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>4087071052</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>3499.14</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/logs/token_usage.xlsx
+++ b/logs/token_usage.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -511,246 +512,213 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>— Лист projects — та же статистика в разрезе проектов (каталогов ~/.claude/projects), отсортировано по стоимости.</t>
+          <t>— Доля использования, % — доля строки в токенах периода (по столбцу «Токены всего»).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>— Лист projects — та же статистика в разрезе проектов (каталогов ~/.claude/projects), отсортировано по стоимости.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>— Данные начинаются с 2026-06-13 21:06 (локальное); первое окно 14.05.2026-14.06.2026 из-за этого неполное (только вечер 13.06).</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Период</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Модель</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Запросов</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Сессий</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Output</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Cache write</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Cache read</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Токены всего</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Cache read, %</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Output/запрос</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Стоимость по API, $</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>$/запрос</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>$/сессию</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Доля стоимости, %</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Доля использования, %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>14.05.2026-14.06.2026</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sonnet</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="3" t="n">
         <v>293</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>587</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>330161</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G15" s="3" t="n">
         <v>940158</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H15" s="3" t="n">
         <v>29047611</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I15" s="3" t="n">
         <v>30318517</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" t="n">
         <v>95.8</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" t="n">
         <v>1127</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
         <v>17.19</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" t="n">
         <v>0.0587</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N15" t="n">
         <v>8.6</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O15" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="P15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>14.05.2026-14.06.2026</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C16" s="4" t="n">
         <v>293</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D16" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E16" s="4" t="n">
         <v>587</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F16" s="4" t="n">
         <v>330161</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>940158</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>29047611</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I16" s="4" t="n">
         <v>30318517</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J16" s="2" t="n">
         <v>95.8</v>
       </c>
-      <c r="K15" s="2" t="n">
+      <c r="K16" s="2" t="n">
         <v>1127</v>
       </c>
-      <c r="L15" s="2" t="n">
+      <c r="L16" s="2" t="n">
         <v>17.19</v>
       </c>
-      <c r="M15" s="2" t="n">
+      <c r="M16" s="2" t="n">
         <v>0.0587</v>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N16" s="2" t="n">
         <v>8.6</v>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O16" s="2" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>14.06.2026-14.07.2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Haiku</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>894</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>39981</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>379130</v>
-      </c>
-      <c r="G16" s="3" t="n">
-        <v>3723871</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>37694487</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>41837469</v>
-      </c>
-      <c r="J16" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>424</v>
-      </c>
-      <c r="L16" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0116</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.3</v>
+      <c r="P16" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -761,47 +729,50 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sonnet</t>
+          <t>Haiku</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>11735</v>
+        <v>894</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>994918</v>
+        <v>39981</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>6998103</v>
+        <v>379130</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>58542938</v>
+        <v>3723871</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>2389456064</v>
+        <v>37694487</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2455992023</v>
+        <v>41837469</v>
       </c>
       <c r="J17" t="n">
-        <v>97.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>596</v>
+        <v>424</v>
       </c>
       <c r="L17" t="n">
-        <v>1044.33</v>
+        <v>10.36</v>
       </c>
       <c r="M17" t="n">
-        <v>0.089</v>
+        <v>0.0116</v>
       </c>
       <c r="N17" t="n">
-        <v>9.67</v>
+        <v>0.4</v>
       </c>
       <c r="O17" t="n">
-        <v>29.8</v>
+        <v>0.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -812,47 +783,50 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Opus</t>
+          <t>Sonnet</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1933</v>
+        <v>11735</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>753138</v>
+        <v>994918</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2140997</v>
+        <v>6998103</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>17579863</v>
+        <v>58542938</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>324661964</v>
+        <v>2389456064</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>345135962</v>
+        <v>2455992023</v>
       </c>
       <c r="J18" t="n">
-        <v>94.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="K18" t="n">
-        <v>1108</v>
+        <v>596</v>
       </c>
       <c r="L18" t="n">
-        <v>329.5</v>
+        <v>1044.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1705</v>
+        <v>0.089</v>
       </c>
       <c r="N18" t="n">
-        <v>9.15</v>
+        <v>9.67</v>
       </c>
       <c r="O18" t="n">
-        <v>9.4</v>
+        <v>29.8</v>
+      </c>
+      <c r="P18" t="n">
+        <v>60.1</v>
       </c>
     </row>
     <row r="19">
@@ -863,97 +837,157 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>Opus</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1933</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>753138</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>2140997</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>17579863</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>324661964</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>345135962</v>
+      </c>
+      <c r="J19" t="n">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1108</v>
+      </c>
+      <c r="L19" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1705</v>
+      </c>
+      <c r="N19" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14.06.2026-14.07.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Fable</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C20" s="3" t="n">
         <v>5565</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>52</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>932714</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>6229760</v>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G20" s="3" t="n">
         <v>48451946</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H20" s="3" t="n">
         <v>1188491178</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I20" s="3" t="n">
         <v>1244105598</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>95.5</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>1119</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L20" t="n">
         <v>2114.96</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M20" t="n">
         <v>0.38</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N20" t="n">
         <v>40.67</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O20" t="n">
         <v>60.4</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="P20" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>14.06.2026-14.07.2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C21" s="4" t="n">
         <v>20127</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D21" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>2720751</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F21" s="4" t="n">
         <v>15747990</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>128298618</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>3940303693</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I21" s="4" t="n">
         <v>4087071052</v>
       </c>
-      <c r="J20" s="2" t="n">
+      <c r="J21" s="2" t="n">
         <v>96.40000000000001</v>
       </c>
-      <c r="K20" s="2" t="n">
+      <c r="K21" s="2" t="n">
         <v>782</v>
       </c>
-      <c r="L20" s="2" t="n">
+      <c r="L21" s="2" t="n">
         <v>3499.14</v>
       </c>
-      <c r="M20" s="2" t="n">
+      <c r="M21" s="2" t="n">
         <v>0.1739</v>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N21" s="2" t="n">
         <v>25.92</v>
       </c>
-      <c r="O20" s="2" t="n">
+      <c r="O21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="2" t="n">
         <v>100</v>
       </c>
     </row>
@@ -968,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -982,6 +1016,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1048,6 +1083,11 @@
           <t>Доля стоимости, %</t>
         </is>
       </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Доля использования, %</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1087,6 +1127,9 @@
       <c r="K4" t="n">
         <v>100</v>
       </c>
+      <c r="L4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1126,6 +1169,9 @@
       <c r="K5" s="2" t="n">
         <v>100</v>
       </c>
+      <c r="L5" s="2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1165,6 +1211,9 @@
       <c r="K6" t="n">
         <v>56.2</v>
       </c>
+      <c r="L6" t="n">
+        <v>32.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1204,6 +1253,9 @@
       <c r="K7" t="n">
         <v>24.4</v>
       </c>
+      <c r="L7" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1243,6 +1295,9 @@
       <c r="K8" t="n">
         <v>19</v>
       </c>
+      <c r="L8" t="n">
+        <v>18.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1282,6 +1337,9 @@
       <c r="K9" t="n">
         <v>0.2</v>
       </c>
+      <c r="L9" t="n">
+        <v>0.3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1321,6 +1379,9 @@
       <c r="K10" t="n">
         <v>0.2</v>
       </c>
+      <c r="L10" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1358,6 +1419,9 @@
         <v>3499.14</v>
       </c>
       <c r="K11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L11" s="2" t="n">
         <v>100</v>
       </c>
     </row>

--- a/logs/token_usage.xlsx
+++ b/logs/token_usage.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -991,6 +991,276 @@
         <v>100</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Haiku</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>4416</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>132</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>305222</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2464243</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>16151174</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>193147112</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>212067751</v>
+      </c>
+      <c r="J22" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>558</v>
+      </c>
+      <c r="L22" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sonnet</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>44802</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>247</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1036550</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>33939421</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>208635057</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>7774333901</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>8017944929</v>
+      </c>
+      <c r="J23" t="n">
+        <v>97</v>
+      </c>
+      <c r="K23" t="n">
+        <v>758</v>
+      </c>
+      <c r="L23" t="n">
+        <v>3626.88</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="O23" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="P23" t="n">
+        <v>44.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Opus</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>20701</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>667884</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>20674784</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>111852782</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>4557226510</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>4690421960</v>
+      </c>
+      <c r="J24" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>999</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3497.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="N24" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="O24" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="P24" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Fable</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>14636</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>236</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>262018</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>14703737</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>108757496</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>5116021312</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>5239744563</v>
+      </c>
+      <c r="J25" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1005</v>
+      </c>
+      <c r="L25" t="n">
+        <v>7213.3</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="N25" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="O25" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="P25" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>84555</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>2271674</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>71782185</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>445396509</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>17640728835</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>18160179203</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>849</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>14390.21</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1002,7 +1272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1425,6 +1695,6768 @@
         <v>100</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>D--AO3-tests</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>38469</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1297618</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>30226159</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>208308617</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>6984796217</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>7224628611</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5348.88</v>
+      </c>
+      <c r="K12" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>39.8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-Operating-System-for-LLMs</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>22688</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>600280</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>21478449</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>141639199</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>5611732483</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>5775450411</v>
+      </c>
+      <c r="J13" t="n">
+        <v>5276.19</v>
+      </c>
+      <c r="K13" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>31.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>D--AI-CRM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>6654</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>50712</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>4302398</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>16730033</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>2710728359</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>2731811502</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1690.76</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D--Dog</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>5849</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>116329</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>5300717</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>37252130</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>1319544633</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1362213809</v>
+      </c>
+      <c r="J15" t="n">
+        <v>827.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-Linked-in</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2277</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>157916</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>1322223</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>7730278</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>551896677</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>561107094</v>
+      </c>
+      <c r="J16" t="n">
+        <v>682.27</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runH1-set2-H-H-ta</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1097</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>440836</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1824854</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>30873483</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>33140270</v>
+      </c>
+      <c r="J17" t="n">
+        <v>40.08</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run6-set2-fable-B-t1</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>356</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>925</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>466847</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1618402</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>28138191</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>30224365</v>
+      </c>
+      <c r="J18" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run5-set2-sonnet-B-t1</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>612</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1598</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>528359</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>1948109</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>45229897</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>47707963</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.91</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run6-set2-fable-C-t1</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>299</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>584</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>339615</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>1328852</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>13678439</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>15347490</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runH1-set2-C-C-ta</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>542</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>214499</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>993508</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>11182178</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>12390727</v>
+      </c>
+      <c r="J21" t="n">
+        <v>18.28</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run6-set2-fable-A-t1</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>95398</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>271353</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>5662630</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>6029565</v>
+      </c>
+      <c r="J22" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run5-set2-sonnet-C-t1</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>183</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>365</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>243136</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>1003508</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>8207187</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>9454196</v>
+      </c>
+      <c r="J23" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run12-set1-fullgates-Ffg1-t1</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>104</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>105435</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>419541</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>6191906</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>6717078</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-Bfg4-t1</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>149</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>406</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>148938</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>714539</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>9828753</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>10692636</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run9-set1-dietv3-Bdiet3-t3</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>179600</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>497083</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>8435633</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>9112637</v>
+      </c>
+      <c r="J26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10b-set1-fullgates-Bfg2-t1</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>124929</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>658470</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>10474844</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>11258467</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run12-set1-fullgates-Ffg1-t2</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>55504</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>237552</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>4735687</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>5029160</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run12-set1-fullgates-Ffg1-t3</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>65271</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>262588</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>3856612</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>4184700</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B0-t3</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>241</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>74877</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>196932</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>3442918</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>3714968</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run19-set1-kernel-Bkn4-t1</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>162647</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>465011</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>3817279</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>4445085</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B0-t1</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>117</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>64032</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>200493</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>3293259</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>3557901</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-C-t3</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>72431</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>198767</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>2826866</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>3098228</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run11-set1-fullgates-Bfg3-t1</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>367</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>123189</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>383142</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>4697187</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>5203885</v>
+      </c>
+      <c r="J34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-Bfg4-t2</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>423</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>116487</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>338682</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>7539629</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>7995221</v>
+      </c>
+      <c r="J35" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run5-set2-sonnet-A-t1</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>285</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>105163</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>348792</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>6554575</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>7008815</v>
+      </c>
+      <c r="J36" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B-t1</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>65164</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>201493</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>2721041</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>2987794</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run8-set1-dietv2-Bdiet2-t1</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>228</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>112775</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>331542</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>3844653</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>4289198</v>
+      </c>
+      <c r="J38" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4b2-v010-sonnet-B-t1</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>82058</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>294634</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>4633137</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>5010016</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bdiet-t3</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>3637</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>105574</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>326836</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>5016452</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>5452499</v>
+      </c>
+      <c r="J40" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B-t3</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>199</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>53736</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>169671</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>2469662</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>2693268</v>
+      </c>
+      <c r="J41" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run16-set1-kernel-Bkn2-t1</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>153</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>94218</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>337522</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>4678854</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>5110747</v>
+      </c>
+      <c r="J42" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-C-t2</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>88649</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>354418</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>2624255</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>3067467</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run14-set1-criticlite-Bcl1-t1</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>77</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>2738</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>102265</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>394551</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>4105620</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>4605174</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B-t2</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>275</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>63255</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>163044</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>2092702</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>2319276</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3b2-v020-sonnet-B-t1</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>71132</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>347028</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>5343431</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>5761761</v>
+      </c>
+      <c r="J46" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bdiet-t1</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>96937</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>297216</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>4805709</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>5200058</v>
+      </c>
+      <c r="J47" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run17-set1-kernel-Bkn3-t2</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>292</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>80712</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>317228</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>3294634</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>3692866</v>
+      </c>
+      <c r="J48" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10b-set1-fullgates-Bfg2-t2</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>399</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>73336</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>251970</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>3752756</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>4078461</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-C-C-t2</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>95594</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>367996</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>3515493</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>3979251</v>
+      </c>
+      <c r="J50" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bfull-t3</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>85105</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>273247</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>3639321</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>3997986</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bfull-t1</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>91115</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>280466</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>3552929</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>3924633</v>
+      </c>
+      <c r="J52" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-C-t3</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>46412</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>153371</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>1812913</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>2012797</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-C-t2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>105675</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>360634</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>2453545</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>2919992</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run17-set1-kernel-Bkn3-t3</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>77985</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>246470</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>4739725</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>5064301</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D--Improving-AI</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>25508</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>86246</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>1541880</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>1653677</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run15-set1-kernel-Bkn1-t1</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>8567</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>75199</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>278217</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>3441031</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>3803014</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-C-t3</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>57117</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>198482</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>2230323</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>2486062</v>
+      </c>
+      <c r="J58" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10-set1-fullgates-Bfg-t1</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>500</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>75231</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>313615</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>3748360</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>4137706</v>
+      </c>
+      <c r="J59" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-C-t2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>61859</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>240920</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>2195014</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>2497915</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run16-set1-kernel-Bkn2-t2</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>392</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>70885</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>247930</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>4647017</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>4966224</v>
+      </c>
+      <c r="J61" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run14-set1-criticlite-Bcl1-t2</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>414</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>79017</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>253178</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>5289288</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>5621897</v>
+      </c>
+      <c r="J62" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run11-set1-fullgates-Bfg3-t2</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>77401</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>209050</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>3787256</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>4074011</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run8-set1-dietv2-Bdiet2-t2</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>72574</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>247708</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>3935015</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>4255670</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4c2-v010-sonnet-C-t2</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>91813</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>305203</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>3126572</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>3523750</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run15-set1-kernel-Bkn1-t2</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>291</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>62681</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>277889</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>2517296</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>2858157</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run16-set1-kernel-Bkn2-t3</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>65770</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>236547</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>4187043</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>4489518</v>
+      </c>
+      <c r="J67" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-B-t3</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>107</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>69670</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>253962</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>4942875</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>5266947</v>
+      </c>
+      <c r="J68" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runH1-set2-H-H-tb</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>28778</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>130386</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>1482752</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>1641974</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-B-t3</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>33778</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>157946</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>1721140</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>1912936</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-C-t2</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>138</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>99531</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>312849</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>2154390</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>2566908</v>
+      </c>
+      <c r="J71" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run17-set1-kernel-Bkn3-t1</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>62291</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>210348</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>2188245</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>2460958</v>
+      </c>
+      <c r="J72" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run9-set1-dietv3-Bdiet3-t1</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>53954</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>235001</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>3224424</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>3513497</v>
+      </c>
+      <c r="J73" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10b-set1-fullgates-Bfg2-t3</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>279</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>66374</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>210603</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>3244666</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>3521922</v>
+      </c>
+      <c r="J74" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runH1-set2-C-C-tb</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>55574</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>240831</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>809083</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>1105548</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>127375</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>242866</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>6238389</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>6610140</v>
+      </c>
+      <c r="J76" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run19-set1-kernel-Bkn4-t3</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>62608</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>286497</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>2970943</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>3320322</v>
+      </c>
+      <c r="J77" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run8-set1-dietv2-Bdiet2-t3</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>121</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>83964</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>197833</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>2608558</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>2890476</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD4-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>81</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>63553</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>189001</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>2461687</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>2714322</v>
+      </c>
+      <c r="J79" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD5-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>79927</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>143544</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>2982988</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>3206529</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-B-t1</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>31012</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>126140</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>1105450</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>1262655</v>
+      </c>
+      <c r="J81" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run15-set1-kernel-Bkn1-t3</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>56581</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>208112</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>2726185</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>2991112</v>
+      </c>
+      <c r="J82" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD6-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>63372</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>124246</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>1499849</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>1687525</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run14-set1-criticlite-Bcl1-t3</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>204</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>45907</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>189888</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>2479946</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>2715945</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-C-C-t2</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>189197</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>2219505</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>2455175</v>
+      </c>
+      <c r="J85" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-Bfg4-t3</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>168838</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>2072491</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>2287723</v>
+      </c>
+      <c r="J86" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>48354</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>142163</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>1828030</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>2018612</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-C-t1</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>75</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>28867</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>172165</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>1053346</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>1254453</v>
+      </c>
+      <c r="J88" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-A-t2</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>46689</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>151643</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>2470710</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2669142</v>
+      </c>
+      <c r="J89" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-C-t3</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>44818</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>199752</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>1142958</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>1387596</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run11-set1-fullgates-Bfg3-t3</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>6498</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>53646</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>190101</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>2304677</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>2554922</v>
+      </c>
+      <c r="J91" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-C-t1</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>44154</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>121699</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>456654</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>622543</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3c2-v020-sonnet-C-t2</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>38617</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>237562</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>1348146</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>1624411</v>
+      </c>
+      <c r="J93" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>71</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>40841</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>119261</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>1985296</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>2145469</v>
+      </c>
+      <c r="J94" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-B0-t2</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>269</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>23913</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>91614</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>1521534</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>1637330</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>533</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>96980</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>196707</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>4189270</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>4483490</v>
+      </c>
+      <c r="J96" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3c2-v020-sonnet-C-t1</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>60831</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>174824</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>650957</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>886656</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13c2-set1-fullgates-C2-t2</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>41218</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>167153</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>1251017</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>1459470</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-C-t3</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>23643</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>107640</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>926533</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>1057889</v>
+      </c>
+      <c r="J99" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run19-set1-kernel-Bkn4-t2</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>43137</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>164598</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>2903853</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>3111920</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4c2-v010-sonnet-C-t1</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>53956</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>116035</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>548098</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>718121</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-C-C-t1</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>41518</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>134542</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>822970</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>999078</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-C-C-t3</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>32991</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>118562</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>2071334</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>2222979</v>
+      </c>
+      <c r="J103" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-C-C-t2</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>31497</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>164725</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>1392539</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>1588831</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-B-t2</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>17818</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>80642</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>899976</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>998599</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3c2-v020-sonnet-C-t3</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>37109</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>156459</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>1344092</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>1537746</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bfull-t2</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>1015</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>33502</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>149107</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>2258295</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>2441919</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-C-t3</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>30824</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>138386</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>1383780</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>1553068</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run9-set1-dietv3-Bdiet3-t2</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>304</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>37497</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>109399</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>1896935</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>2044135</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10-set1-fullgates-Bfg-t2</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>32406</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>149839</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>3203300</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>3385946</v>
+      </c>
+      <c r="J110" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-C-C-t3</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>24131</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>173013</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>1215581</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>1412797</v>
+      </c>
+      <c r="J111" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-Dsn-D-t1</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>38246</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>97148</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>1472601</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>1608045</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>21188</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>109490</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>1059548</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>1190281</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-A-t2</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>10879</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>31320</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>625111</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>667338</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-Bdiet-t2</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>36887</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>123696</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>1867971</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>2028820</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-t150-dod-smoke</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>29728</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>312464</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>1442562</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>1784985</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-C-t1</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>20011</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>140798</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>950265</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>1111142</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run7-set1-diet-C-t1</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>26266</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>123757</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>746768</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>896849</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13c2-set1-fullgates-C2-t1</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>24367</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>140783</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>507053</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>672239</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-B-t2</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>248</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>30797</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>121407</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>2767723</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>2920175</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-A-t2</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>9367</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>33104</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>495873</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>538367</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-C-C-t1</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>25228</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>129047</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>404502</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>558809</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-B-t3</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>22577</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>127793</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>1370645</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>1521069</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-C-C-t1</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>18917</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>146880</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>323787</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>489608</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-probe</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>2103</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>68506</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>350657</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>421294</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13c2-set1-fullgates-C2-t3</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>26771</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>90323</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>1156962</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>1274128</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD6-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>14282</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>69243</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>1144515</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>1228094</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-C-C-t3</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>21124</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>83848</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>1059035</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>1164071</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD4-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>15184</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>93653</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>847965</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>956842</v>
+      </c>
+      <c r="J129" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Aop-A-t2</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>13065</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>61976</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>432372</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>507435</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-A-t2</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>17526</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>51408</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>1676734</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>1745726</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD5-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>16815</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>65824</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>995576</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>1078259</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-B-t2</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>27009</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>83772</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>1830040</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>1941145</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Aop-A-t3</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>11475</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>52814</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>505825</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>570142</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4c2-v010-sonnet-C-t3</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>17745</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>91644</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>698112</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>807551</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD4-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>59</v>
+      </c>
+      <c r="D136" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>470</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>42953</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>109623</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>2719616</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>2872662</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD1-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="D137" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>532</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>66783</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>132742</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>3338905</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>3538962</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Aop-A-t1</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>8045</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>63451</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>178973</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>250483</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-B-t1</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>17534</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>53523</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>1129851</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>1200941</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-A-t3</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>4972</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>15065</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>348446</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>368502</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-A-t3</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>5317</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>15387</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>275198</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>295917</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release1-A-t1</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>4435</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>28098</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>132889</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>165434</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Asn-A-t2</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="D143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>11564</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>48794</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>719518</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>779906</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD6-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="D144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>295</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>30583</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>91794</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>1561557</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>1684229</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD3-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D145" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>13427</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>47038</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>773552</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>834053</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD2-set1-Dsn-D-t3</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>13194</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>40763</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>909576</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>963573</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-A-t1</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>7211</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>68632</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>176104</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>251959</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Asn-A-t1</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>9570</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>42700</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>398951</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>451240</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-A-t2</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>11565</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>34565</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>940693</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>986859</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-C-t2</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="D150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>2851</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>12165</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>280799</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>295832</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-C-t1</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1559</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>32541</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>59839</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>93945</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run10-set1-fullgates-Bfg-t3</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>11279</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>64241</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>409199</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>484735</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run13-set1-fullgates-A-t3</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>6449</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>38498</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>406329</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>451296</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run18-set1-Asn-A-t3</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>9348</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>31420</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>593255</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>634049</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-release2-A-t1</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>4102</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>12402</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>126357</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>142869</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-runD5-set1-Dhk-D-t2</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="D156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>214</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>12064</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>54584</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>1094833</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>1161695</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-C-t2</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>2368</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>13093</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>152066</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>167537</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-t150-critic-smoke</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="D158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>3594</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>51420</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>192012</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>247064</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-A-t1</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>9291</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>23639</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>217762</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>250701</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-t152-dispatch-smoke</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>3764</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>59050</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>367600</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>430466</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-C-t1</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1304</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>9906</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>82262</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>93478</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-kit-smoke</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>1980</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>71318</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>121328</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>194662</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-A-t1</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>7037</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>22958</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>211871</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>241876</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run4-v010-sonnet-A-t3</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>4311</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>16736</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>336342</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>357405</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-B-t1</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>1596</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>50982</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>52580</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D--Improving-AI-exam-run3-v020-sonnet-A-t3</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>3208</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>15354</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>245604</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>264178</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-t132-smoke-polygon-A-t1</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D167" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>829</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>39135</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>83656</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>123656</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-a7822844-34c9-40f9-a2e4-72f4f853d811-scratchpad-smoke-polygon-A-t1</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>242</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>30462</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>30714</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-f4727492-2f64-4dce-b0e7-a2ab0b780218-scratchpad-t152-hook-order-probe</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>313</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>8034</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>54202</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>62567</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-a7822844-34c9-40f9-a2e4-72f4f853d811-scratchpad-accept-smoke-polygon-A-t1</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>173</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>7647</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>22796</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>30626</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>C--Users-user-AppData-Local-Temp-claude-D--Improving-AI-Operating-System-for-LLMs-a7822844-34c9-40f9-a2e4-72f4f853d811-scratchpad-smoke-polygon2-A-t1</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>7615</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>22796</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>30472</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>14.07.2026-14.08.2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>ИТОГО</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="n">
+        <v>84555</v>
+      </c>
+      <c r="D172" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="E172" s="4" t="n">
+        <v>2271674</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>71782185</v>
+      </c>
+      <c r="G172" s="4" t="n">
+        <v>445396509</v>
+      </c>
+      <c r="H172" s="4" t="n">
+        <v>17640728835</v>
+      </c>
+      <c r="I172" s="4" t="n">
+        <v>18160179203</v>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>14390.21</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
